--- a/models_guided_4layer_v2/codebooks_4layer_v2.xlsx
+++ b/models_guided_4layer_v2/codebooks_4layer_v2.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS5"/>
+  <dimension ref="A1:BM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,38 +538,6 @@
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
     <col width="9" customWidth="1" min="65" max="65"/>
-    <col width="9" customWidth="1" min="66" max="66"/>
-    <col width="9" customWidth="1" min="67" max="67"/>
-    <col width="9" customWidth="1" min="68" max="68"/>
-    <col width="9" customWidth="1" min="69" max="69"/>
-    <col width="9" customWidth="1" min="70" max="70"/>
-    <col width="9" customWidth="1" min="71" max="71"/>
-    <col width="9" customWidth="1" min="72" max="72"/>
-    <col width="9" customWidth="1" min="73" max="73"/>
-    <col width="9" customWidth="1" min="74" max="74"/>
-    <col width="9" customWidth="1" min="75" max="75"/>
-    <col width="9" customWidth="1" min="76" max="76"/>
-    <col width="9" customWidth="1" min="77" max="77"/>
-    <col width="9" customWidth="1" min="78" max="78"/>
-    <col width="9" customWidth="1" min="79" max="79"/>
-    <col width="9" customWidth="1" min="80" max="80"/>
-    <col width="9" customWidth="1" min="81" max="81"/>
-    <col width="9" customWidth="1" min="82" max="82"/>
-    <col width="9" customWidth="1" min="83" max="83"/>
-    <col width="9" customWidth="1" min="84" max="84"/>
-    <col width="9" customWidth="1" min="85" max="85"/>
-    <col width="9" customWidth="1" min="86" max="86"/>
-    <col width="9" customWidth="1" min="87" max="87"/>
-    <col width="9" customWidth="1" min="88" max="88"/>
-    <col width="9" customWidth="1" min="89" max="89"/>
-    <col width="9" customWidth="1" min="90" max="90"/>
-    <col width="9" customWidth="1" min="91" max="91"/>
-    <col width="9" customWidth="1" min="92" max="92"/>
-    <col width="9" customWidth="1" min="93" max="93"/>
-    <col width="9" customWidth="1" min="94" max="94"/>
-    <col width="9" customWidth="1" min="95" max="95"/>
-    <col width="9" customWidth="1" min="96" max="96"/>
-    <col width="9" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -770,102 +738,6 @@
       <c r="BM1" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="BN1" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="BO1" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="BP1" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="BQ1" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="BR1" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="BS1" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="BT1" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="BU1" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="BV1" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="BW1" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="BX1" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="BY1" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ1" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="CA1" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="CB1" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="CC1" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="CD1" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="CE1" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="CF1" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="CG1" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="CH1" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="CI1" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="CJ1" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="CK1" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="CL1" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="CM1" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="CN1" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="CO1" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="CP1" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="CQ1" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="CR1" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="CS1" s="1" t="n">
-        <v>95</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1065,38 +937,6 @@
       <c r="BM2" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="BN2" s="2" t="inlineStr"/>
-      <c r="BO2" s="2" t="inlineStr"/>
-      <c r="BP2" s="2" t="inlineStr"/>
-      <c r="BQ2" s="2" t="inlineStr"/>
-      <c r="BR2" s="2" t="inlineStr"/>
-      <c r="BS2" s="2" t="inlineStr"/>
-      <c r="BT2" s="2" t="inlineStr"/>
-      <c r="BU2" s="2" t="inlineStr"/>
-      <c r="BV2" s="2" t="inlineStr"/>
-      <c r="BW2" s="2" t="inlineStr"/>
-      <c r="BX2" s="2" t="inlineStr"/>
-      <c r="BY2" s="2" t="inlineStr"/>
-      <c r="BZ2" s="2" t="inlineStr"/>
-      <c r="CA2" s="2" t="inlineStr"/>
-      <c r="CB2" s="2" t="inlineStr"/>
-      <c r="CC2" s="2" t="inlineStr"/>
-      <c r="CD2" s="2" t="inlineStr"/>
-      <c r="CE2" s="2" t="inlineStr"/>
-      <c r="CF2" s="2" t="inlineStr"/>
-      <c r="CG2" s="2" t="inlineStr"/>
-      <c r="CH2" s="2" t="inlineStr"/>
-      <c r="CI2" s="2" t="inlineStr"/>
-      <c r="CJ2" s="2" t="inlineStr"/>
-      <c r="CK2" s="2" t="inlineStr"/>
-      <c r="CL2" s="2" t="inlineStr"/>
-      <c r="CM2" s="2" t="inlineStr"/>
-      <c r="CN2" s="2" t="inlineStr"/>
-      <c r="CO2" s="2" t="inlineStr"/>
-      <c r="CP2" s="2" t="inlineStr"/>
-      <c r="CQ2" s="2" t="inlineStr"/>
-      <c r="CR2" s="2" t="inlineStr"/>
-      <c r="CS2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1296,38 +1136,6 @@
       <c r="BM3" s="5" t="n">
         <v>1.997332</v>
       </c>
-      <c r="BN3" s="4" t="inlineStr"/>
-      <c r="BO3" s="4" t="inlineStr"/>
-      <c r="BP3" s="4" t="inlineStr"/>
-      <c r="BQ3" s="4" t="inlineStr"/>
-      <c r="BR3" s="4" t="inlineStr"/>
-      <c r="BS3" s="4" t="inlineStr"/>
-      <c r="BT3" s="4" t="inlineStr"/>
-      <c r="BU3" s="4" t="inlineStr"/>
-      <c r="BV3" s="4" t="inlineStr"/>
-      <c r="BW3" s="4" t="inlineStr"/>
-      <c r="BX3" s="4" t="inlineStr"/>
-      <c r="BY3" s="4" t="inlineStr"/>
-      <c r="BZ3" s="4" t="inlineStr"/>
-      <c r="CA3" s="4" t="inlineStr"/>
-      <c r="CB3" s="4" t="inlineStr"/>
-      <c r="CC3" s="4" t="inlineStr"/>
-      <c r="CD3" s="4" t="inlineStr"/>
-      <c r="CE3" s="4" t="inlineStr"/>
-      <c r="CF3" s="4" t="inlineStr"/>
-      <c r="CG3" s="4" t="inlineStr"/>
-      <c r="CH3" s="4" t="inlineStr"/>
-      <c r="CI3" s="4" t="inlineStr"/>
-      <c r="CJ3" s="4" t="inlineStr"/>
-      <c r="CK3" s="4" t="inlineStr"/>
-      <c r="CL3" s="4" t="inlineStr"/>
-      <c r="CM3" s="4" t="inlineStr"/>
-      <c r="CN3" s="4" t="inlineStr"/>
-      <c r="CO3" s="4" t="inlineStr"/>
-      <c r="CP3" s="4" t="inlineStr"/>
-      <c r="CQ3" s="4" t="inlineStr"/>
-      <c r="CR3" s="4" t="inlineStr"/>
-      <c r="CS3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1336,292 +1144,196 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>-0.1389</v>
+        <v>-0.136</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>-0.1367</v>
+        <v>-0.1273</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-0.136</v>
+        <v>-0.126</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>-0.1312</v>
+        <v>-0.1174</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>-0.1305</v>
+        <v>-0.1098</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-0.126</v>
+        <v>-0.1021</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>-0.125261</v>
+        <v>-0.1008</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>-0.1242</v>
+        <v>-0.0926</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>-0.1134</v>
+        <v>-0.0916</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>-0.113</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>-0.1087</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>-0.1079</v>
+        <v>-0.0823</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>-0.1027</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>-0.1021</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="P4" s="7" t="n">
-        <v>-0.1019</v>
+        <v>-0.0805</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>-0.1012</v>
+        <v>-0.071504</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>-0.1008</v>
+        <v>-0.062029</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>-0.1001</v>
+        <v>-0.05641</v>
       </c>
       <c r="T4" s="7" t="n">
-        <v>-0.0939</v>
+        <v>-0.053584</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>-0.0936</v>
+        <v>-0.051758</v>
       </c>
       <c r="V4" s="7" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.046246</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>-0.0886</v>
+        <v>-0.043316</v>
       </c>
       <c r="X4" s="7" t="n">
-        <v>-0.073916</v>
+        <v>-0.040124</v>
       </c>
       <c r="Y4" s="7" t="n">
-        <v>-0.064416</v>
+        <v>-0.034696</v>
       </c>
       <c r="Z4" s="7" t="n">
-        <v>-0.064415</v>
+        <v>-0.029822</v>
       </c>
       <c r="AA4" s="7" t="n">
-        <v>-0.064414</v>
+        <v>-0.025268</v>
       </c>
       <c r="AB4" s="7" t="n">
-        <v>-0.06411600000000001</v>
+        <v>-0.020503</v>
       </c>
       <c r="AC4" s="7" t="n">
-        <v>-0.063916</v>
+        <v>-0.016966</v>
       </c>
       <c r="AD4" s="7" t="n">
-        <v>-0.062106</v>
+        <v>-0.014691</v>
       </c>
       <c r="AE4" s="7" t="n">
-        <v>-0.060516</v>
+        <v>-0.011686</v>
       </c>
       <c r="AF4" s="7" t="n">
-        <v>-0.060416</v>
+        <v>-0.008971</v>
       </c>
       <c r="AG4" s="7" t="n">
-        <v>-0.060016</v>
+        <v>-0.006208</v>
       </c>
       <c r="AH4" s="7" t="n">
-        <v>-0.059716</v>
+        <v>-0.003533</v>
       </c>
       <c r="AI4" s="7" t="n">
-        <v>-0.059516</v>
+        <v>-0.002274</v>
       </c>
       <c r="AJ4" s="7" t="n">
-        <v>-0.058816</v>
+        <v>-0.001474</v>
       </c>
       <c r="AK4" s="7" t="n">
-        <v>-0.046516</v>
+        <v>0.001357</v>
       </c>
       <c r="AL4" s="7" t="n">
-        <v>-0.046116</v>
+        <v>0.001883</v>
       </c>
       <c r="AM4" s="7" t="n">
-        <v>-0.045916</v>
+        <v>0.002483</v>
       </c>
       <c r="AN4" s="7" t="n">
-        <v>-0.042716</v>
+        <v>0.003428</v>
       </c>
       <c r="AO4" s="7" t="n">
-        <v>-0.036316</v>
+        <v>0.004752</v>
       </c>
       <c r="AP4" s="7" t="n">
-        <v>-0.034468</v>
+        <v>0.006541</v>
       </c>
       <c r="AQ4" s="7" t="n">
-        <v>-0.031147</v>
+        <v>0.008292000000000001</v>
       </c>
       <c r="AR4" s="7" t="n">
-        <v>-0.028366</v>
+        <v>0.010887</v>
       </c>
       <c r="AS4" s="7" t="n">
-        <v>-0.025721</v>
+        <v>0.014076</v>
       </c>
       <c r="AT4" s="7" t="n">
-        <v>-0.020163</v>
+        <v>0.017038</v>
       </c>
       <c r="AU4" s="7" t="n">
-        <v>-0.017346</v>
+        <v>0.020418</v>
       </c>
       <c r="AV4" s="7" t="n">
-        <v>-0.015546</v>
+        <v>0.024632</v>
       </c>
       <c r="AW4" s="7" t="n">
-        <v>-0.012135</v>
+        <v>0.029149</v>
       </c>
       <c r="AX4" s="7" t="n">
-        <v>-0.010476</v>
+        <v>0.03388</v>
       </c>
       <c r="AY4" s="7" t="n">
-        <v>-0.008574999999999999</v>
+        <v>0.039112</v>
       </c>
       <c r="AZ4" s="7" t="n">
-        <v>-0.006499</v>
+        <v>0.045026</v>
       </c>
       <c r="BA4" s="7" t="n">
-        <v>-0.004606</v>
+        <v>0.050753</v>
       </c>
       <c r="BB4" s="7" t="n">
-        <v>-0.003182</v>
+        <v>0.055363</v>
       </c>
       <c r="BC4" s="7" t="n">
-        <v>-0.002122</v>
+        <v>0.060071</v>
       </c>
       <c r="BD4" s="7" t="n">
-        <v>-0.001411</v>
+        <v>0.065188</v>
       </c>
       <c r="BE4" s="7" t="n">
-        <v>0.001215</v>
+        <v>0.070601</v>
       </c>
       <c r="BF4" s="7" t="n">
-        <v>0.001554</v>
+        <v>0.07619099999999999</v>
       </c>
       <c r="BG4" s="7" t="n">
-        <v>0.001886</v>
+        <v>0.1384</v>
       </c>
       <c r="BH4" s="7" t="n">
-        <v>0.002245</v>
+        <v>0.1389</v>
       </c>
       <c r="BI4" s="7" t="n">
-        <v>0.002738</v>
+        <v>0.139352</v>
       </c>
       <c r="BJ4" s="7" t="n">
-        <v>0.003544</v>
+        <v>0.147252</v>
       </c>
       <c r="BK4" s="7" t="n">
-        <v>0.004715</v>
+        <v>0.147691</v>
       </c>
       <c r="BL4" s="7" t="n">
-        <v>0.005989</v>
+        <v>0.193439</v>
       </c>
       <c r="BM4" s="7" t="n">
-        <v>0.007371</v>
-      </c>
-      <c r="BN4" s="7" t="n">
-        <v>0.008585000000000001</v>
-      </c>
-      <c r="BO4" s="7" t="n">
-        <v>0.010494</v>
-      </c>
-      <c r="BP4" s="7" t="n">
-        <v>0.012513</v>
-      </c>
-      <c r="BQ4" s="7" t="n">
-        <v>0.014543</v>
-      </c>
-      <c r="BR4" s="7" t="n">
-        <v>0.016597</v>
-      </c>
-      <c r="BS4" s="7" t="n">
-        <v>0.018915</v>
-      </c>
-      <c r="BT4" s="7" t="n">
-        <v>0.020967</v>
-      </c>
-      <c r="BU4" s="7" t="n">
-        <v>0.024206</v>
-      </c>
-      <c r="BV4" s="7" t="n">
-        <v>0.029429</v>
-      </c>
-      <c r="BW4" s="7" t="n">
-        <v>0.084552</v>
-      </c>
-      <c r="BX4" s="7" t="n">
-        <v>0.08905200000000001</v>
-      </c>
-      <c r="BY4" s="7" t="n">
-        <v>0.0897</v>
-      </c>
-      <c r="BZ4" s="7" t="n">
-        <v>0.109252</v>
-      </c>
-      <c r="CA4" s="7" t="n">
-        <v>0.1095</v>
-      </c>
-      <c r="CB4" s="7" t="n">
-        <v>0.109852</v>
-      </c>
-      <c r="CC4" s="7" t="n">
-        <v>0.109952</v>
-      </c>
-      <c r="CD4" s="7" t="n">
-        <v>0.114952</v>
-      </c>
-      <c r="CE4" s="7" t="n">
-        <v>0.116052</v>
-      </c>
-      <c r="CF4" s="7" t="n">
-        <v>0.1389</v>
-      </c>
-      <c r="CG4" s="7" t="n">
-        <v>0.139352</v>
-      </c>
-      <c r="CH4" s="7" t="n">
-        <v>0.140552</v>
-      </c>
-      <c r="CI4" s="7" t="n">
-        <v>0.140852</v>
-      </c>
-      <c r="CJ4" s="7" t="n">
-        <v>0.141452</v>
-      </c>
-      <c r="CK4" s="7" t="n">
-        <v>0.141552</v>
-      </c>
-      <c r="CL4" s="7" t="n">
-        <v>0.141553</v>
-      </c>
-      <c r="CM4" s="7" t="n">
-        <v>0.141652</v>
-      </c>
-      <c r="CN4" s="7" t="n">
-        <v>0.147252</v>
-      </c>
-      <c r="CO4" s="7" t="n">
-        <v>0.147352</v>
-      </c>
-      <c r="CP4" s="7" t="n">
-        <v>0.147452</v>
-      </c>
-      <c r="CQ4" s="7" t="n">
-        <v>0.147552</v>
-      </c>
-      <c r="CR4" s="7" t="n">
-        <v>0.147691</v>
-      </c>
-      <c r="CS4" s="7" t="n">
-        <v>0.147891</v>
+        <v>0.205139</v>
       </c>
     </row>
     <row r="5">
@@ -1631,292 +1343,196 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>-0.027366</v>
+        <v>-0.030535</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>-0.026591</v>
+        <v>-0.029903</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>-0.025911</v>
+        <v>-0.028724</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>-0.025253</v>
+        <v>-0.027203</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>-0.024728</v>
+        <v>-0.025693</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.024293</v>
+        <v>-0.024496</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>-0.023984</v>
+        <v>-0.023448</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-0.023621</v>
+        <v>-0.022709</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>-0.02327</v>
+        <v>-0.021931</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>-0.022401</v>
+        <v>-0.020747</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>-0.021063</v>
+        <v>-0.020083</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>-0.020606</v>
+        <v>-0.019663</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>-0.020605</v>
+        <v>-0.018228</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>-0.020179</v>
+        <v>-0.017224</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>-0.019202</v>
+        <v>-0.016281</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>-0.018806</v>
+        <v>-0.015131</v>
       </c>
       <c r="R5" s="9" t="n">
-        <v>-0.018306</v>
+        <v>-0.014512</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>-0.017956</v>
+        <v>-0.013206</v>
       </c>
       <c r="T5" s="9" t="n">
-        <v>-0.016859</v>
+        <v>-0.012284</v>
       </c>
       <c r="U5" s="9" t="n">
-        <v>-0.016347</v>
+        <v>-0.011298</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>-0.015711</v>
+        <v>-0.010174</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>-0.015252</v>
+        <v>-0.009386</v>
       </c>
       <c r="X5" s="9" t="n">
-        <v>-0.01479</v>
+        <v>-0.008503999999999999</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>-0.013639</v>
+        <v>-0.006872</v>
       </c>
       <c r="Z5" s="9" t="n">
-        <v>-0.012863</v>
+        <v>-0.005488</v>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>-0.012038</v>
+        <v>-0.00428</v>
       </c>
       <c r="AB5" s="9" t="n">
-        <v>-0.011488</v>
+        <v>-0.00375</v>
       </c>
       <c r="AC5" s="9" t="n">
-        <v>-0.010861</v>
+        <v>-0.003286</v>
       </c>
       <c r="AD5" s="9" t="n">
-        <v>-0.010368</v>
+        <v>-0.002751</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>-0.009833</v>
+        <v>-0.002253</v>
       </c>
       <c r="AF5" s="9" t="n">
-        <v>-0.009272000000000001</v>
+        <v>-0.001752</v>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>-0.008755000000000001</v>
+        <v>-0.001241</v>
       </c>
       <c r="AH5" s="9" t="n">
-        <v>-0.008259000000000001</v>
+        <v>0.001212</v>
       </c>
       <c r="AI5" s="9" t="n">
-        <v>-0.00758</v>
+        <v>0.001578</v>
       </c>
       <c r="AJ5" s="9" t="n">
-        <v>-0.007206</v>
+        <v>0.002078</v>
       </c>
       <c r="AK5" s="9" t="n">
-        <v>-0.006846</v>
+        <v>0.002585</v>
       </c>
       <c r="AL5" s="9" t="n">
-        <v>-0.006011</v>
+        <v>0.003313</v>
       </c>
       <c r="AM5" s="9" t="n">
-        <v>-0.005312</v>
+        <v>0.003799</v>
       </c>
       <c r="AN5" s="9" t="n">
-        <v>-0.004753</v>
+        <v>0.00422</v>
       </c>
       <c r="AO5" s="9" t="n">
-        <v>-0.004311</v>
+        <v>0.004635</v>
       </c>
       <c r="AP5" s="9" t="n">
-        <v>-0.003901</v>
+        <v>0.005279</v>
       </c>
       <c r="AQ5" s="9" t="n">
-        <v>-0.003445</v>
+        <v>0.00623</v>
       </c>
       <c r="AR5" s="9" t="n">
-        <v>-0.003034</v>
+        <v>0.006961</v>
       </c>
       <c r="AS5" s="9" t="n">
-        <v>-0.002695</v>
+        <v>0.007479</v>
       </c>
       <c r="AT5" s="9" t="n">
-        <v>-0.002327</v>
+        <v>0.008361</v>
       </c>
       <c r="AU5" s="9" t="n">
-        <v>-0.001745</v>
+        <v>0.009442000000000001</v>
       </c>
       <c r="AV5" s="9" t="n">
-        <v>-0.001176</v>
+        <v>0.010342</v>
       </c>
       <c r="AW5" s="9" t="n">
-        <v>0.001232</v>
+        <v>0.011202</v>
       </c>
       <c r="AX5" s="9" t="n">
-        <v>0.001716</v>
+        <v>0.012542</v>
       </c>
       <c r="AY5" s="9" t="n">
-        <v>0.002007</v>
+        <v>0.013612</v>
       </c>
       <c r="AZ5" s="9" t="n">
-        <v>0.002388</v>
+        <v>0.014915</v>
       </c>
       <c r="BA5" s="9" t="n">
-        <v>0.002839</v>
+        <v>0.01656</v>
       </c>
       <c r="BB5" s="9" t="n">
-        <v>0.003091</v>
+        <v>0.017777</v>
       </c>
       <c r="BC5" s="9" t="n">
-        <v>0.003776</v>
+        <v>0.019726</v>
       </c>
       <c r="BD5" s="9" t="n">
-        <v>0.004429</v>
+        <v>0.020819</v>
       </c>
       <c r="BE5" s="9" t="n">
-        <v>0.005023</v>
+        <v>0.021802</v>
       </c>
       <c r="BF5" s="9" t="n">
-        <v>0.005319</v>
+        <v>0.023055</v>
       </c>
       <c r="BG5" s="9" t="n">
-        <v>0.005666</v>
+        <v>0.024152</v>
       </c>
       <c r="BH5" s="9" t="n">
-        <v>0.005876</v>
+        <v>0.025485</v>
       </c>
       <c r="BI5" s="9" t="n">
-        <v>0.006198</v>
+        <v>0.026672</v>
       </c>
       <c r="BJ5" s="9" t="n">
-        <v>0.006773</v>
+        <v>0.02817</v>
       </c>
       <c r="BK5" s="9" t="n">
-        <v>0.007296</v>
+        <v>0.028929</v>
       </c>
       <c r="BL5" s="9" t="n">
-        <v>0.00769</v>
+        <v>0.02976</v>
       </c>
       <c r="BM5" s="9" t="n">
-        <v>0.008099</v>
-      </c>
-      <c r="BN5" s="9" t="n">
-        <v>0.008751</v>
-      </c>
-      <c r="BO5" s="9" t="n">
-        <v>0.00927</v>
-      </c>
-      <c r="BP5" s="9" t="n">
-        <v>0.009664000000000001</v>
-      </c>
-      <c r="BQ5" s="9" t="n">
-        <v>0.010087</v>
-      </c>
-      <c r="BR5" s="9" t="n">
-        <v>0.010899</v>
-      </c>
-      <c r="BS5" s="9" t="n">
-        <v>0.011564</v>
-      </c>
-      <c r="BT5" s="9" t="n">
-        <v>0.01252</v>
-      </c>
-      <c r="BU5" s="9" t="n">
-        <v>0.013519</v>
-      </c>
-      <c r="BV5" s="9" t="n">
-        <v>0.014012</v>
-      </c>
-      <c r="BW5" s="9" t="n">
-        <v>0.014565</v>
-      </c>
-      <c r="BX5" s="9" t="n">
-        <v>0.015268</v>
-      </c>
-      <c r="BY5" s="9" t="n">
-        <v>0.015703</v>
-      </c>
-      <c r="BZ5" s="9" t="n">
-        <v>0.016506</v>
-      </c>
-      <c r="CA5" s="9" t="n">
-        <v>0.017452</v>
-      </c>
-      <c r="CB5" s="9" t="n">
-        <v>0.018171</v>
-      </c>
-      <c r="CC5" s="9" t="n">
-        <v>0.019099</v>
-      </c>
-      <c r="CD5" s="9" t="n">
-        <v>0.01979</v>
-      </c>
-      <c r="CE5" s="9" t="n">
-        <v>0.020363</v>
-      </c>
-      <c r="CF5" s="9" t="n">
-        <v>0.020974</v>
-      </c>
-      <c r="CG5" s="9" t="n">
-        <v>0.021423</v>
-      </c>
-      <c r="CH5" s="9" t="n">
-        <v>0.021517</v>
-      </c>
-      <c r="CI5" s="9" t="n">
-        <v>0.021889</v>
-      </c>
-      <c r="CJ5" s="9" t="n">
-        <v>0.022461</v>
-      </c>
-      <c r="CK5" s="9" t="n">
-        <v>0.02296</v>
-      </c>
-      <c r="CL5" s="9" t="n">
-        <v>0.023596</v>
-      </c>
-      <c r="CM5" s="9" t="n">
-        <v>0.024138</v>
-      </c>
-      <c r="CN5" s="9" t="n">
-        <v>0.02458</v>
-      </c>
-      <c r="CO5" s="9" t="n">
-        <v>0.025283</v>
-      </c>
-      <c r="CP5" s="9" t="n">
-        <v>0.025783</v>
-      </c>
-      <c r="CQ5" s="9" t="n">
-        <v>0.026437</v>
-      </c>
-      <c r="CR5" s="9" t="n">
-        <v>0.02698</v>
-      </c>
-      <c r="CS5" s="9" t="n">
-        <v>0.027371</v>
+        <v>0.030723</v>
       </c>
     </row>
   </sheetData>
